--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8EC742-1406-4736-B6AE-298DF3C914B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F7EA3-5768-4F25-B0C5-4DE1929DB8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="-15030" windowWidth="15855" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="-14895" windowWidth="15855" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
@@ -439,20 +439,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F7EA3-5768-4F25-B0C5-4DE1929DB8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5DFC77-E1B4-4926-8980-34DEB38763C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="-14895" windowWidth="15855" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="-14835" windowWidth="17865" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
@@ -433,9 +433,23 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5DFC77-E1B4-4926-8980-34DEB38763C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C4109-1464-41A6-9E4D-EEFB12AC6EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="-14835" windowWidth="17865" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7755" yWindow="-13410" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -450,7 +450,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
